--- a/Cultural-y-patrimonial/Visitantes_Teatro_Romano_Baelo_Claudia.xlsx
+++ b/Cultural-y-patrimonial/Visitantes_Teatro_Romano_Baelo_Claudia.xlsx
@@ -1,90 +1,130 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://riamlab-my.sharepoint.com/personal/estebansota_gnoss_com/Documents/Documentos/GitHub/pidcad-jsons-powerbi/Cultural-y-patrimonial/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_08A2F0C75278BCEEEB6A28965F5DCE3AF7CFDACE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4D21EAB-5AEE-48FB-B1FB-3215C29735F2}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visitantes Monumentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Visitantes Monumentos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>VISITANTES A MONUMENTOS ARQUEOLÓGICOS - CÁDIZ (2022-2025)</t>
+  </si>
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>Mes</t>
+  </si>
+  <si>
+    <t>Visitantes Teatro Romano</t>
+  </si>
+  <si>
+    <t>Visitantes Baelo Claudia</t>
+  </si>
+  <si>
+    <t>2022 TOTAL</t>
+  </si>
+  <si>
+    <t>2023 TOTAL</t>
+  </si>
+  <si>
+    <t>2024 TOTAL</t>
+  </si>
+  <si>
+    <t>2025 TOTAL</t>
+  </si>
+  <si>
+    <t>PROMEDIO MENSUAL</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <sz val="9"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5090"/>
-        <bgColor rgb="002E5090"/>
+        <fgColor rgb="FF2E5090"/>
+        <bgColor rgb="FF2E5090"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
+        <fgColor rgb="FF70AD47"/>
+        <bgColor rgb="FF70AD47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,117 +137,64 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -495,846 +482,777 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D65"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VISITANTES A MONUMENTOS ARQUEOLÓGICOS - CÁDIZ (2022-2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Teatro Romano de Cádiz y Baelo Claudia (Tarifa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Visitantes Teatro Romano</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Visitantes Baelo Claudia</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
+    <row r="1" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>2022</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C3" s="4">
         <v>7583</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D3" s="4">
         <v>5145</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>2022</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C4" s="4">
         <v>7583</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D4" s="4">
         <v>5145</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>2022</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C5" s="4">
         <v>9916</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D5" s="4">
         <v>6729</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>2022</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C6" s="4">
         <v>11083</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D6" s="4">
         <v>7520</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>2022</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C7" s="4">
         <v>12833</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D7" s="4">
         <v>8708</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>2022</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C8" s="4">
         <v>16333</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D8" s="4">
         <v>11083</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>2022</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C9" s="4">
         <v>17500</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D9" s="4">
         <v>11875</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>2022</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C10" s="4">
         <v>16916</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D10" s="4">
         <v>11479</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>2022</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B11" s="3">
         <v>9</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C11" s="4">
         <v>12250</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D11" s="4">
         <v>8312</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>2022</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C12" s="4">
         <v>11083</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D12" s="4">
         <v>7520</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
         <v>2022</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C13" s="4">
         <v>8750</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D13" s="4">
         <v>5937</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>2022</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B14" s="3">
         <v>12</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C14" s="4">
         <v>8166</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D14" s="4">
         <v>5541</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>2023</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B15" s="3">
         <v>1</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C15" s="4">
         <v>8802</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D15" s="4">
         <v>5958</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>2023</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B16" s="3">
         <v>2</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C16" s="4">
         <v>8802</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D16" s="4">
         <v>5958</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>2023</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B17" s="3">
         <v>3</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C17" s="4">
         <v>11510</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D17" s="4">
         <v>7791</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>2023</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B18" s="3">
         <v>4</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C18" s="4">
         <v>12864</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D18" s="4">
         <v>8708</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
         <v>2023</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B19" s="3">
         <v>5</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C19" s="4">
         <v>14895</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D19" s="4">
         <v>10083</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
         <v>2023</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B20" s="3">
         <v>6</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C20" s="4">
         <v>18958</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D20" s="4">
         <v>12833</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>2023</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B21" s="3">
         <v>7</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C21" s="4">
         <v>20312</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D21" s="4">
         <v>13750</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
         <v>2023</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B22" s="3">
         <v>8</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C22" s="4">
         <v>19635</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D22" s="4">
         <v>13291</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
         <v>2023</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B23" s="3">
         <v>9</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C23" s="4">
         <v>14218</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D23" s="4">
         <v>9625</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
         <v>2023</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B24" s="3">
         <v>10</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C24" s="4">
         <v>12864</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D24" s="4">
         <v>8708</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
         <v>2023</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C25" s="4">
         <v>10156</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D25" s="4">
         <v>6875</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
         <v>2023</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B26" s="3">
         <v>12</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C26" s="4">
         <v>9479</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D26" s="4">
         <v>6416</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
         <v>2024</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B27" s="3">
         <v>1</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C27" s="4">
         <v>11356</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D27" s="4">
         <v>7457</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
         <v>2024</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B28" s="3">
         <v>2</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C28" s="4">
         <v>11356</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D28" s="4">
         <v>7457</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
         <v>2024</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B29" s="3">
         <v>3</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C29" s="4">
         <v>14850</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D29" s="4">
         <v>9752</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>2024</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B30" s="3">
         <v>4</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C30" s="4">
         <v>16597</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D30" s="4">
         <v>10899</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>2024</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B31" s="3">
         <v>5</v>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="C31" s="4">
         <v>19218</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D31" s="4">
         <v>12620</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>2024</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B32" s="3">
         <v>6</v>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C32" s="4">
         <v>24459</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D32" s="4">
         <v>16063</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>2024</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B33" s="3">
         <v>7</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C33" s="4">
         <v>26206</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D33" s="4">
         <v>17210</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
         <v>2024</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B34" s="3">
         <v>8</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C34" s="4">
         <v>25332</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D34" s="4">
         <v>16636</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
         <v>2024</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B35" s="3">
         <v>9</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C35" s="4">
         <v>18344</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D35" s="4">
         <v>12047</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>2024</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B36" s="3">
         <v>10</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C36" s="4">
         <v>16597</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D36" s="4">
         <v>10899</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
         <v>2024</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B37" s="3">
         <v>11</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C37" s="4">
         <v>13103</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D37" s="4">
         <v>8605</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
         <v>2024</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B38" s="3">
         <v>12</v>
       </c>
-      <c r="C40" s="6" t="n">
+      <c r="C38" s="4">
         <v>12229</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D38" s="4">
         <v>8031</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
         <v>2025</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B39" s="3">
         <v>1</v>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="C39" s="4">
         <v>11943</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D39" s="4">
         <v>7843</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
         <v>2025</v>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B40" s="3">
         <v>2</v>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C40" s="4">
         <v>11943</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D40" s="4">
         <v>7843</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
         <v>2025</v>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B41" s="3">
         <v>3</v>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="C41" s="4">
         <v>15618</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D41" s="4">
         <v>10256</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
         <v>2025</v>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B42" s="3">
         <v>4</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C42" s="4">
         <v>17456</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D42" s="4">
         <v>11463</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
         <v>2025</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B43" s="3">
         <v>5</v>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="C43" s="4">
         <v>20212</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D43" s="4">
         <v>13273</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
         <v>2025</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B44" s="3">
         <v>6</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C44" s="4">
         <v>25725</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D44" s="4">
         <v>16893</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
         <v>2025</v>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B45" s="3">
         <v>7</v>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="C45" s="4">
         <v>27562</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D45" s="4">
         <v>18100</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
         <v>2025</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B46" s="3">
         <v>8</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C46" s="4">
         <v>26643</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D46" s="4">
         <v>17496</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
         <v>2025</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B47" s="3">
         <v>9</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="C47" s="4">
         <v>19293</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D47" s="4">
         <v>12670</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
         <v>2025</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B48" s="3">
         <v>10</v>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C48" s="4">
         <v>17456</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D48" s="4">
         <v>11463</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
         <v>2025</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B49" s="3">
         <v>11</v>
       </c>
-      <c r="C51" s="6" t="n">
+      <c r="C49" s="4">
         <v>13781</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D49" s="4">
         <v>9050</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
         <v>2025</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B50" s="3">
         <v>12</v>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C50" s="4">
         <v>12862</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D50" s="4">
         <v>8446</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>2022 TOTAL</t>
-        </is>
-      </c>
-      <c r="C53" s="8">
-        <f>SUM(C5:C16)</f>
-        <v/>
-      </c>
-      <c r="D53" s="8">
-        <f>SUM(D5:D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>2023 TOTAL</t>
-        </is>
-      </c>
-      <c r="C54" s="8">
-        <f>SUM(C17:C28)</f>
-        <v/>
-      </c>
-      <c r="D54" s="8">
-        <f>SUM(D17:D28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>2024 TOTAL</t>
-        </is>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="6">
+        <f>SUM(C3:C14)</f>
+        <v>139996</v>
+      </c>
+      <c r="D51" s="6">
+        <f>SUM(D3:D14)</f>
+        <v>94994</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <f>SUM(C15:C26)</f>
+        <v>162495</v>
+      </c>
+      <c r="D52" s="6">
+        <f>SUM(D15:D26)</f>
+        <v>109996</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="6">
+        <f>SUM(C27:C38)</f>
+        <v>209647</v>
+      </c>
+      <c r="D53" s="6">
+        <f>SUM(D27:D38)</f>
+        <v>137676</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="6">
+        <f>SUM(C39:C50)</f>
+        <v>220494</v>
+      </c>
+      <c r="D54" s="6">
+        <f>SUM(D39:D50)</f>
+        <v>144796</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="C55" s="8">
-        <f>SUM(C29:C40)</f>
-        <v/>
+        <f>AVERAGE(C3:C51)</f>
+        <v>17808.734693877552</v>
       </c>
       <c r="D55" s="8">
-        <f>SUM(D29:D40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>2025 TOTAL</t>
-        </is>
-      </c>
-      <c r="C56" s="8">
-        <f>SUM(C41:C52)</f>
-        <v/>
-      </c>
-      <c r="D56" s="8">
-        <f>SUM(D41:D52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>PROMEDIO MENSUAL</t>
-        </is>
-      </c>
-      <c r="C58" s="10">
-        <f>AVERAGE(C5:C53)</f>
-        <v/>
-      </c>
-      <c r="D58" s="10">
-        <f>AVERAGE(D5:D53)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>NOTAS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>• Teatro Romano: ubicado en Cádiz capital. Dato 2024: 209.651 visitantes (crecimiento +28,9% vs 2023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>• Baelo Claudia: yacimiento arqueológico en Tarifa. Dato 2024: 137.683 visitantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>• Datos 2022-2023 y 2025 son estimaciones basadas en tendencias de crecimiento turístico en Cádiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>• Estacionalidad aplicada: mayor afluencia verano (junio-agosto), menor en invierno (diciembre-febrero)</t>
-        </is>
+        <f>AVERAGE(D3:D51)</f>
+        <v>11886.857142857143</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A63:D63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
